--- a/frontend/test_data/header_detection/Pivoted_Data_Test.xlsx
+++ b/frontend/test_data/header_detection/Pivoted_Data_Test.xlsx
@@ -475,7 +475,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:M6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -494,18 +494,27 @@
         <v>Consistent String Signal</v>
       </c>
       <c r="F1" t="str">
+        <v>Consistent Numeric Signal</v>
+      </c>
+      <c r="G1" t="str">
         <v>Pure Data Penalty</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
+        <v>Numeric Data Penalty</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Pivoted Series Bonus</v>
+      </c>
+      <c r="J1" t="str">
         <v>100% String Bonus</v>
       </c>
-      <c r="H1" t="str">
+      <c r="K1" t="str">
         <v>Unique Values Rule</v>
       </c>
-      <c r="I1" t="str">
+      <c r="L1" t="str">
         <v>Orphan Header Penalty</v>
       </c>
-      <c r="J1" t="str">
+      <c r="M1" t="str">
         <v>TOTAL SCORE</v>
       </c>
     </row>
@@ -529,15 +538,24 @@
         <v>0</v>
       </c>
       <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
         <v>10</v>
       </c>
-      <c r="H2">
+      <c r="K2">
         <v>5</v>
       </c>
-      <c r="I2">
-        <v>0</v>
-      </c>
-      <c r="J2">
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
         <v>36</v>
       </c>
     </row>
@@ -561,15 +579,24 @@
         <v>0</v>
       </c>
       <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
         <v>10</v>
       </c>
-      <c r="H3">
+      <c r="K3">
         <v>5</v>
       </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
         <v>36</v>
       </c>
     </row>
@@ -584,25 +611,34 @@
         <v>6</v>
       </c>
       <c r="D4">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E4">
+        <v>15</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>10</v>
+      </c>
+      <c r="K4">
         <v>5</v>
       </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <v>10</v>
-      </c>
-      <c r="H4">
-        <v>5</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>56</v>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>36</v>
       </c>
     </row>
     <row r="5">
@@ -616,25 +652,34 @@
         <v>6</v>
       </c>
       <c r="D5">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E5">
+        <v>3</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>10</v>
+      </c>
+      <c r="K5">
         <v>5</v>
       </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <v>10</v>
-      </c>
-      <c r="H5">
-        <v>5</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>56</v>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>42</v>
       </c>
     </row>
     <row r="6">
@@ -651,27 +696,36 @@
         <v>0</v>
       </c>
       <c r="E6">
+        <v>3</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>-50</v>
+      </c>
+      <c r="H6">
+        <v>-20</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
         <v>5</v>
       </c>
-      <c r="F6">
-        <v>-50</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>5</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>-34</v>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>-56</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M6"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/frontend/test_data/header_detection/Pivoted_Data_Test.xlsx
+++ b/frontend/test_data/header_detection/Pivoted_Data_Test.xlsx
@@ -475,7 +475,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:N6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -485,37 +485,40 @@
         <v>Row Preview</v>
       </c>
       <c r="C1" t="str">
-        <v>Density Bonus</v>
+        <v>Pillar 1: Density (%)</v>
       </c>
       <c r="D1" t="str">
-        <v>Data Boundary Signal</v>
+        <v>Pillar 2: Boundary (%)</v>
       </c>
       <c r="E1" t="str">
-        <v>Consistent String Signal</v>
+        <v>Pillar 3: Consistency (%)</v>
       </c>
       <c r="F1" t="str">
-        <v>Consistent Numeric Signal</v>
+        <v>Pillar 4: Traits (%)</v>
       </c>
       <c r="G1" t="str">
         <v>Pure Data Penalty</v>
       </c>
       <c r="H1" t="str">
-        <v>Numeric Data Penalty</v>
+        <v>Mixed Data Penalty</v>
       </c>
       <c r="I1" t="str">
-        <v>Pivoted Series Bonus</v>
+        <v>Search Booster (Pivoted)</v>
       </c>
       <c r="J1" t="str">
-        <v>100% String Bonus</v>
+        <v>Orphan Header Penalty</v>
       </c>
       <c r="K1" t="str">
-        <v>Unique Values Rule</v>
+        <v>Duplicates Penalty</v>
       </c>
       <c r="L1" t="str">
-        <v>Orphan Header Penalty</v>
+        <v>FILLED CELLS</v>
       </c>
       <c r="M1" t="str">
-        <v>TOTAL SCORE</v>
+        <v>TOTAL RAW SCORE</v>
+      </c>
+      <c r="N1" t="str">
+        <v>NORMALIZED SCORE (%)</v>
       </c>
     </row>
     <row r="2">
@@ -526,17 +529,17 @@
         <v>["Vendor ID","V001","V002"]</v>
       </c>
       <c r="C2">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
+        <v>35</v>
+      </c>
+      <c r="F2">
         <v>15</v>
       </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
       <c r="G2">
         <v>0</v>
       </c>
@@ -547,16 +550,19 @@
         <v>0</v>
       </c>
       <c r="J2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M2">
-        <v>36</v>
+        <v>70</v>
+      </c>
+      <c r="N2">
+        <v>70</v>
       </c>
     </row>
     <row r="3">
@@ -567,17 +573,17 @@
         <v>["Company Name","Acme","Globex"]</v>
       </c>
       <c r="C3">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
+        <v>35</v>
+      </c>
+      <c r="F3">
         <v>15</v>
       </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
       <c r="G3">
         <v>0</v>
       </c>
@@ -588,16 +594,19 @@
         <v>0</v>
       </c>
       <c r="J3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M3">
-        <v>36</v>
+        <v>70</v>
+      </c>
+      <c r="N3">
+        <v>70</v>
       </c>
     </row>
     <row r="4">
@@ -608,17 +617,17 @@
         <v>["City","Austin","New York"]</v>
       </c>
       <c r="C4">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
       <c r="E4">
+        <v>35</v>
+      </c>
+      <c r="F4">
         <v>15</v>
       </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
       <c r="G4">
         <v>0</v>
       </c>
@@ -629,16 +638,19 @@
         <v>0</v>
       </c>
       <c r="J4">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K4">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M4">
-        <v>36</v>
+        <v>70</v>
+      </c>
+      <c r="N4">
+        <v>70</v>
       </c>
     </row>
     <row r="5">
@@ -649,37 +661,40 @@
         <v>["State","TX","NY"]</v>
       </c>
       <c r="C5">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="D5">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="E5">
+        <v>7</v>
+      </c>
+      <c r="F5">
+        <v>15</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
         <v>3</v>
       </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>10</v>
-      </c>
-      <c r="K5">
-        <v>5</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
       <c r="M5">
-        <v>42</v>
+        <v>82</v>
+      </c>
+      <c r="N5">
+        <v>82</v>
       </c>
     </row>
     <row r="6">
@@ -690,42 +705,45 @@
         <v>["Invoice Total","5000","12000"]</v>
       </c>
       <c r="C6">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="D6">
         <v>0</v>
       </c>
       <c r="E6">
+        <v>7</v>
+      </c>
+      <c r="F6">
+        <v>5</v>
+      </c>
+      <c r="G6">
+        <v>-100</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
         <v>3</v>
       </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>-50</v>
-      </c>
-      <c r="H6">
-        <v>-20</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <v>5</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
       <c r="M6">
-        <v>-56</v>
+        <v>-68</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N6"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/frontend/test_data/header_detection/Pivoted_Data_Test.xlsx
+++ b/frontend/test_data/header_detection/Pivoted_Data_Test.xlsx
@@ -475,7 +475,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:M6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -503,21 +503,18 @@
         <v>Mixed Data Penalty</v>
       </c>
       <c r="I1" t="str">
-        <v>Search Booster (Pivoted)</v>
+        <v>Orphan Header Penalty</v>
       </c>
       <c r="J1" t="str">
-        <v>Orphan Header Penalty</v>
+        <v>Duplicates Penalty</v>
       </c>
       <c r="K1" t="str">
-        <v>Duplicates Penalty</v>
+        <v>FILLED CELLS</v>
       </c>
       <c r="L1" t="str">
-        <v>FILLED CELLS</v>
+        <v>TOTAL RAW SCORE</v>
       </c>
       <c r="M1" t="str">
-        <v>TOTAL RAW SCORE</v>
-      </c>
-      <c r="N1" t="str">
         <v>NORMALIZED SCORE (%)</v>
       </c>
     </row>
@@ -553,15 +550,12 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L2">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="M2">
-        <v>70</v>
-      </c>
-      <c r="N2">
         <v>70</v>
       </c>
     </row>
@@ -597,15 +591,12 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L3">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="M3">
-        <v>70</v>
-      </c>
-      <c r="N3">
         <v>70</v>
       </c>
     </row>
@@ -641,15 +632,12 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L4">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="M4">
-        <v>70</v>
-      </c>
-      <c r="N4">
         <v>70</v>
       </c>
     </row>
@@ -685,15 +673,12 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L5">
-        <v>3</v>
+        <v>82</v>
       </c>
       <c r="M5">
-        <v>82</v>
-      </c>
-      <c r="N5">
         <v>82</v>
       </c>
     </row>
@@ -729,21 +714,18 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L6">
-        <v>3</v>
+        <v>-68</v>
       </c>
       <c r="M6">
-        <v>-68</v>
-      </c>
-      <c r="N6">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M6"/>
   </ignoredErrors>
 </worksheet>
 </file>